--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -468,7 +468,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>JEFATURA ZONAL DE JUNIN</v>
+        <v>JEFTURA ZONAL DE JUNIN</v>
       </c>
       <c r="C3" t="str">
         <v>31/03/2026</v>
@@ -480,7 +480,7 @@
         <v>INICIAL DE LICENCIA DE USO</v>
       </c>
       <c r="F3" t="str">
-        <v>46724112</v>
+        <v>77276891</v>
       </c>
       <c r="G3" t="str">
         <v>029042-0</v>
@@ -576,7 +576,7 @@
         <v>INICIAL DE LICENCIA DE USO</v>
       </c>
       <c r="F6" t="str">
-        <v>46724112</v>
+        <v>77276891</v>
       </c>
       <c r="G6" t="str">
         <v>029042-0</v>
@@ -608,7 +608,7 @@
         <v>INICIAL DE LICENCIA DE USO</v>
       </c>
       <c r="F7" t="str">
-        <v>46724112</v>
+        <v>77276891</v>
       </c>
       <c r="G7" t="str">
         <v>029042-0</v>
@@ -623,9 +623,14 @@
         <v>Pendiente</v>
       </c>
     </row>
+    <row r="11">
+      <c r="D11" t="str">
+        <v>s</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -480,7 +480,7 @@
         <v>INICIAL DE LICENCIA DE USO</v>
       </c>
       <c r="F3" t="str">
-        <v>77276891</v>
+        <v>46724112</v>
       </c>
       <c r="G3" t="str">
         <v>029042-0</v>

--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,28 +430,31 @@
       <c r="J1" t="str">
         <v>estado</v>
       </c>
+      <c r="K1" t="str">
+        <v>observaciones</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>JEFATURA ZONAL DE JUNIN</v>
+        <v>LIMA</v>
       </c>
       <c r="C2" t="str">
-        <v>31/03/2026</v>
+        <v>31/3/26</v>
       </c>
       <c r="D2" t="str">
-        <v>10:00-10:15</v>
+        <v>12:30-12:45</v>
       </c>
       <c r="E2" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
+        <v>RENOVACIÓN DE LICENCIA DE USO</v>
       </c>
       <c r="F2" t="str">
-        <v>46724112</v>
+        <v>44136452</v>
       </c>
       <c r="G2" t="str">
-        <v>029042-0</v>
+        <v>052340-0</v>
       </c>
       <c r="H2" t="str">
         <v>CORTA</v>
@@ -494,28 +497,31 @@
       <c r="J3" t="str">
         <v>Pendiente</v>
       </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>JEFATURA ZONAL LAMBAYEQUE (EX-INTENDENCIA II NORTE)</v>
+        <v>JEFATURA ZONAL DE JUNIN</v>
       </c>
       <c r="C4" t="str">
-        <v>31/3/26</v>
+        <v>31/03/2026</v>
       </c>
       <c r="D4" t="str">
-        <v>08:30-08:45</v>
+        <v>10:00-10:15</v>
       </c>
       <c r="E4" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
+        <v>INICIAL DE LICENCIA DE USO</v>
       </c>
       <c r="F4" t="str">
-        <v>77276891</v>
+        <v>46724112</v>
       </c>
       <c r="G4" t="str">
-        <v>090086-0</v>
+        <v>029042-0</v>
       </c>
       <c r="H4" t="str">
         <v>CORTA</v>
@@ -525,6 +531,9 @@
       </c>
       <c r="J4" t="str">
         <v>Pendiente</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -550,87 +559,26 @@
         <v>090086-0</v>
       </c>
       <c r="H5" t="str">
-        <v>LARGA</v>
+        <v>CORTA</v>
       </c>
       <c r="I5" t="str">
-        <v>ESCOPETA</v>
+        <v>REVOLVER</v>
       </c>
       <c r="J5" t="str">
         <v>Pendiente</v>
       </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>JEFTURA ZONAL DE JUNIN</v>
-      </c>
-      <c r="C6" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="D6" t="str">
-        <v>10:00-10:15</v>
-      </c>
-      <c r="E6" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="F6" t="str">
-        <v>77276891</v>
-      </c>
-      <c r="G6" t="str">
-        <v>029042-0</v>
-      </c>
-      <c r="H6" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="I6" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Pendiente</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
-        <v>JEFTURA ZONAL DE JUNIN</v>
-      </c>
-      <c r="C7" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="D7" t="str">
-        <v>10:00-10:15</v>
-      </c>
-      <c r="E7" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="F7" t="str">
-        <v>77276891</v>
-      </c>
-      <c r="G7" t="str">
-        <v>029042-0</v>
-      </c>
-      <c r="H7" t="str">
-        <v>LARGA</v>
-      </c>
-      <c r="I7" t="str">
-        <v>ESCOPETA</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Pendiente</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="D11" t="str">
-        <v>s</v>
+      <c r="K6" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -1,58 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +245,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +279,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,234 +414,298 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>id_registro</v>
-      </c>
-      <c r="B1" t="str">
-        <v>sede</v>
-      </c>
-      <c r="C1" t="str">
-        <v>fecha</v>
-      </c>
-      <c r="D1" t="str">
-        <v>hora_rango</v>
-      </c>
-      <c r="E1" t="str">
-        <v>tipo_operacion</v>
-      </c>
-      <c r="F1" t="str">
-        <v>doc_vigilante</v>
-      </c>
-      <c r="G1" t="str">
-        <v>nro_solicitud</v>
-      </c>
-      <c r="H1" t="str">
-        <v>tipo_arma</v>
-      </c>
-      <c r="I1" t="str">
-        <v>arma</v>
-      </c>
-      <c r="J1" t="str">
-        <v>estado</v>
-      </c>
-      <c r="K1" t="str">
-        <v>observaciones</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_registro</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sede</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>hora_rango</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_operacion</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>doc_vigilante</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>nro_solicitud</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_arma</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>arma</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>LIMA</v>
-      </c>
-      <c r="C2" t="str">
-        <v>31/3/26</v>
-      </c>
-      <c r="D2" t="str">
-        <v>12:30-12:45</v>
-      </c>
-      <c r="E2" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="F2" t="str">
-        <v>44136452</v>
-      </c>
-      <c r="G2" t="str">
-        <v>052340-0</v>
-      </c>
-      <c r="H2" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="I2" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Pendiente</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>31/3/26</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12:30-12:45</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>44136452</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>052340-0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>No alcanzo cupo para horario 12:30-12:45</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>JEFTURA ZONAL DE JUNIN</v>
-      </c>
-      <c r="C3" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="D3" t="str">
-        <v>10:00-10:15</v>
-      </c>
-      <c r="E3" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="F3" t="str">
-        <v>46724112</v>
-      </c>
-      <c r="G3" t="str">
-        <v>029042-0</v>
-      </c>
-      <c r="H3" t="str">
-        <v>LARGA</v>
-      </c>
-      <c r="I3" t="str">
-        <v>ESCOPETA</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Pendiente</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JEFTURA ZONAL DE JUNIN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10:00-10:15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>INICIAL DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>46724112</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>029042-0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LARGA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ESCOPETA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>JEFATURA ZONAL DE JUNIN</v>
-      </c>
-      <c r="C4" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="D4" t="str">
-        <v>10:00-10:15</v>
-      </c>
-      <c r="E4" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="F4" t="str">
-        <v>46724112</v>
-      </c>
-      <c r="G4" t="str">
-        <v>029042-0</v>
-      </c>
-      <c r="H4" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="I4" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Pendiente</v>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE JUNIN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10:00-10:15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>INICIAL DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>46724112</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>029042-0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>JEFATURA ZONAL LAMBAYEQUE (EX-INTENDENCIA II NORTE)</v>
-      </c>
-      <c r="C5" t="str">
-        <v>31/3/26</v>
-      </c>
-      <c r="D5" t="str">
-        <v>08:30-08:45</v>
-      </c>
-      <c r="E5" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="F5" t="str">
-        <v>77276891</v>
-      </c>
-      <c r="G5" t="str">
-        <v>090086-0</v>
-      </c>
-      <c r="H5" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="I5" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Pendiente</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="K6" t="str">
-        <v/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL LAMBAYEQUE (EX-INTENDENCIA II NORTE)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>31/3/26</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>08:30-08:45</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>77276891</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>090086-0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>No alcanzo cupo para horario 08:30-08:45</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -1,58 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +245,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +279,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,247 +414,377 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>id_registro</v>
-      </c>
-      <c r="B1" t="str">
-        <v>sede</v>
-      </c>
-      <c r="C1" t="str">
-        <v>fecha</v>
-      </c>
-      <c r="D1" t="str">
-        <v>hora_rango</v>
-      </c>
-      <c r="E1" t="str">
-        <v>fecha_programacion</v>
-      </c>
-      <c r="F1" t="str">
-        <v>tipo_operacion</v>
-      </c>
-      <c r="G1" t="str">
-        <v>doc_vigilante</v>
-      </c>
-      <c r="H1" t="str">
-        <v>nro_solicitud</v>
-      </c>
-      <c r="I1" t="str">
-        <v>tipo_arma</v>
-      </c>
-      <c r="J1" t="str">
-        <v>arma</v>
-      </c>
-      <c r="K1" t="str">
-        <v>estado</v>
-      </c>
-      <c r="L1" t="str">
-        <v>observaciones</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_registro</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ruc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>prioridad</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sede</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>hora_rango</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_programacion</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_operacion</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>doc_vigilante</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>nro_solicitud</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_arma</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>arma</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>LIMA</v>
-      </c>
-      <c r="C2" t="str">
-        <v>31/03/26</v>
-      </c>
-      <c r="D2" t="str">
-        <v>12:30-12:45</v>
-      </c>
-      <c r="E2" t="str">
-        <v>24/03/2026</v>
-      </c>
-      <c r="F2" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="G2" t="str">
-        <v>44136452</v>
-      </c>
-      <c r="H2" t="str">
-        <v>052340-0</v>
-      </c>
-      <c r="I2" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="J2" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Pendiente</v>
-      </c>
-      <c r="L2" t="str">
-        <v>No alcanzo cupo para horario 12:30-12:45</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL LAMBAYEQUE (EX-INTENDENCIA II NORTE)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>07/04/26</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12:45-13:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>77276891</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>090086-0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No alcanzo cupo para horario 12:30-12:45</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>JEFATURA ZONAL DE JUNIN</v>
-      </c>
-      <c r="C3" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="D3" t="str">
-        <v>10:00-10:15</v>
-      </c>
-      <c r="E3" t="str">
-        <v>24/03/2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="G3" t="str">
-        <v>46724112</v>
-      </c>
-      <c r="H3" t="str">
-        <v>029042-0</v>
-      </c>
-      <c r="I3" t="str">
-        <v>LARGA</v>
-      </c>
-      <c r="J3" t="str">
-        <v>ESCOPETA</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Pendiente</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Selva</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE JUNIN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10:00-10:15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>INICIAL DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>46724112</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>029042-0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Documento vigilante no disponible para esta razón social/RUC. DNI=46724112 | RUC=Selva</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>JEFATURA ZONAL DE JUNIN</v>
-      </c>
-      <c r="C4" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="D4" t="str">
-        <v>10:00-10:15</v>
-      </c>
-      <c r="E4" t="str">
-        <v>24/03/2026</v>
-      </c>
-      <c r="F4" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="G4" t="str">
-        <v>46724112</v>
-      </c>
-      <c r="H4" t="str">
-        <v>029042-0</v>
-      </c>
-      <c r="I4" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="J4" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Pendiente</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Selva</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE JUNIN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10:00-10:15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>INICIAL DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>46724112</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>029042-0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>LARGA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ESCOPETA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>JEFATURA ZONAL LAMBAYEQUE (EX-INTENDENCIA II NORTE)</v>
-      </c>
-      <c r="C5" t="str">
-        <v>07/04/26</v>
-      </c>
-      <c r="D5" t="str">
-        <v>12:45-13:00</v>
-      </c>
-      <c r="E5" t="str">
-        <v>25/03/2026</v>
-      </c>
-      <c r="F5" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="G5" t="str">
-        <v>77276891</v>
-      </c>
-      <c r="H5" t="str">
-        <v>090086-0</v>
-      </c>
-      <c r="I5" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="J5" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Pendiente</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>31/03/26</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>12:30-12:45</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>44136452</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>052340-0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No alcanzo cupo para horario 12:30-12:45</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12:45-13:00</t>
+          <t>10:30-10:45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>No alcanzo cupo para horario 12:30-12:45</t>
+          <t>No alcanzo cupo para horario 10:30-10:45</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Selva</t>
+          <t>J &amp; V Resguardo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Documento vigilante no disponible para esta razón social/RUC. DNI=46724112 | RUC=Selva</t>
+          <t>Error en procesamiento: No se encontró Nro Solicitud con token '29042'. Opciones: ['Seleccione']</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Selva</t>
+          <t>J &amp; V Resguardo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -710,7 +710,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Error en procesamiento: No se encontró Nro Solicitud con token '29042'. Opciones: ['Seleccione']</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
